--- a/data/trans_orig/P1426-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1426-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2012</t>
+          <t>Población con diagnóstico de hipoacusia en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9529</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25594</t>
+          <t>25349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24485</t>
+          <t>23591</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43140</t>
+          <t>44469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>677875</t>
+          <t>678120</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>693940</t>
+          <t>694719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>672565</t>
+          <t>673459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>689594</t>
+          <t>689715</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1357379</t>
+          <t>1356050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1382370</t>
+          <t>1380590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>23113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,82 +1090,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>17561</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10043</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27356</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>31121</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>21444</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>45743</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>17561</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9955</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>28604</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>31121</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>21838</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>46346</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>995289</t>
+          <t>994834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1010689</t>
+          <t>1011009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,82 +1203,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1011412</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1001617</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1018930</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1846</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2015800</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2001178</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2025477</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>97,77%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1011412</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1000369</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1019018</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2015800</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>2000575</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2025083</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25445</t>
+          <t>24292</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33372</t>
+          <t>32911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740180</t>
+          <t>741457</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754568</t>
+          <t>754562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>751729</t>
+          <t>752882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>769598</t>
+          <t>769572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1501425</t>
+          <t>1501886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1522258</t>
+          <t>1522195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26635</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13087</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>31240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26865</t>
+          <t>25506</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>48889</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>921104</t>
+          <t>921096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>938582</t>
+          <t>937814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1020518</t>
+          <t>1020661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1038814</t>
+          <t>1038773</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1948537</t>
+          <t>1950751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1972775</t>
+          <t>1974134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39092</t>
+          <t>38818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69570</t>
+          <t>69833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83920</t>
+          <t>83422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97841</t>
+          <t>98274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142573</t>
+          <t>144032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3357209</t>
+          <t>3356946</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3387687</t>
+          <t>3387961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3471178</t>
+          <t>3471676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3505287</t>
+          <t>3504696</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6839304</t>
+          <t>6837845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6884036</t>
+          <t>6883603</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2016</t>
+          <t>Población con diagnóstico de hipoacusia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18740</t>
+          <t>18093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>14093</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31701</t>
+          <t>31917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>656060</t>
+          <t>656707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>669247</t>
+          <t>669853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653261</t>
+          <t>653183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>666890</t>
+          <t>666752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1315938</t>
+          <t>1315722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1333909</t>
+          <t>1333546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19098</t>
+          <t>19276</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16543</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37558</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>24370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48600</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1003333</t>
+          <t>1003155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1017371</t>
+          <t>1017464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1005355</t>
+          <t>1004720</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1026370</t>
+          <t>1026568</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2016744</t>
+          <t>2014921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2040550</t>
+          <t>2040974</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>17247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>25028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>16526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>37236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>741673</t>
+          <t>742305</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754207</t>
+          <t>754118</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>759657</t>
+          <t>759983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>776127</t>
+          <t>776333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1507659</t>
+          <t>1507327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1528244</t>
+          <t>1528037</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31099</t>
+          <t>32247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27742</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53058</t>
+          <t>53621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>909102</t>
+          <t>909064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>927136</t>
+          <t>926385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1012680</t>
+          <t>1011532</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1031226</t>
+          <t>1031140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1928288</t>
+          <t>1927725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1953604</t>
+          <t>1953504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36995</t>
+          <t>36588</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65415</t>
+          <t>65709</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55721</t>
+          <t>57185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90268</t>
+          <t>91946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100457</t>
+          <t>99982</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145200</t>
+          <t>145331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3328935</t>
+          <t>3328641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3357355</t>
+          <t>3357762</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3454274</t>
+          <t>3452596</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3488821</t>
+          <t>3487357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6793692</t>
+          <t>6793561</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6838435</t>
+          <t>6838910</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipoacusia en 2023</t>
+          <t>Población con diagnóstico de hipoacusia en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>31654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50643</t>
+          <t>53488</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33944</t>
+          <t>34814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49543</t>
+          <t>50881</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70552</t>
+          <t>70057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97040</t>
+          <t>95270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>584798</t>
+          <t>581953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603359</t>
+          <t>603787</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>625227</t>
+          <t>623889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>640826</t>
+          <t>639956</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1213172</t>
+          <t>1214942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1239660</t>
+          <t>1240155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26488</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66411</t>
+          <t>65611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36053</t>
+          <t>36002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57122</t>
+          <t>56571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60376</t>
+          <t>62422</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114101</t>
+          <t>114341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1126453</t>
+          <t>1127253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1166376</t>
+          <t>1170054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>900155</t>
+          <t>900706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>921224</t>
+          <t>921275</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2036041</t>
+          <t>2035801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2089766</t>
+          <t>2087720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34565</t>
+          <t>35059</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40873</t>
+          <t>41333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>34002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68508</t>
+          <t>68277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667228</t>
+          <t>666734</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>685787</t>
+          <t>685842</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>891862</t>
+          <t>891402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>919520</t>
+          <t>917959</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1566020</t>
+          <t>1566251</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1601063</t>
+          <t>1600526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30876</t>
+          <t>30559</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53730</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33414</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56684</t>
+          <t>55781</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69660</t>
+          <t>70037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101697</t>
+          <t>100422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873101</t>
+          <t>873979</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>895955</t>
+          <t>896272</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1034438</t>
+          <t>1035341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1057708</t>
+          <t>1057309</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1916256</t>
+          <t>1917531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1948293</t>
+          <t>1947916</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120677</t>
+          <t>118802</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179778</t>
+          <t>179133</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132119</t>
+          <t>130509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182663</t>
+          <t>181385</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>273975</t>
+          <t>272030</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>350189</t>
+          <t>351359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3277152</t>
+          <t>3277797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3336253</t>
+          <t>3338128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3473241</t>
+          <t>3474519</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3523785</t>
+          <t>3525395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6762645</t>
+          <t>6761475</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6838859</t>
+          <t>6840804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1426-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1426-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>26509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23591</t>
+          <t>24274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>18725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44469</t>
+          <t>41310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>678120</t>
+          <t>676960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>694719</t>
+          <t>695139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>673459</t>
+          <t>672776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>689715</t>
+          <t>689353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1356050</t>
+          <t>1359209</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1380590</t>
+          <t>1381794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>23674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27356</t>
+          <t>26542</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21444</t>
+          <t>21017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45743</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>994834</t>
+          <t>994273</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1011009</t>
+          <t>1011424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1001617</t>
+          <t>1002431</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1018930</t>
+          <t>1018997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2001178</t>
+          <t>2003198</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2025477</t>
+          <t>2025904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>24440</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32911</t>
+          <t>33049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>741457</t>
+          <t>741164</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754562</t>
+          <t>754563</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>752882</t>
+          <t>752734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>769572</t>
+          <t>769645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1501886</t>
+          <t>1501748</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1522195</t>
+          <t>1521842</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>30631</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25506</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48889</t>
+          <t>50942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>921096</t>
+          <t>921407</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>937814</t>
+          <t>938544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1020661</t>
+          <t>1021270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1038773</t>
+          <t>1039560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950751</t>
+          <t>1948698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1974134</t>
+          <t>1973982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38818</t>
+          <t>38013</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69833</t>
+          <t>68462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>50236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83422</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>98281</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>144032</t>
+          <t>147293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3356946</t>
+          <t>3358317</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3387961</t>
+          <t>3388766</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3471676</t>
+          <t>3471282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3504696</t>
+          <t>3504862</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6837845</t>
+          <t>6834584</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6883603</t>
+          <t>6883596</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18093</t>
+          <t>17795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>19524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14093</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31917</t>
+          <t>32095</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>656707</t>
+          <t>657005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>669853</t>
+          <t>669417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653183</t>
+          <t>653315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>666752</t>
+          <t>667117</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1315722</t>
+          <t>1315544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1333546</t>
+          <t>1333914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19276</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>36851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24370</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50423</t>
+          <t>50330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1003155</t>
+          <t>1002992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1017464</t>
+          <t>1017577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1004720</t>
+          <t>1006062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1026568</t>
+          <t>1027305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2014921</t>
+          <t>2015014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2040974</t>
+          <t>2040991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17247</t>
+          <t>17765</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8678</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>23732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37236</t>
+          <t>37289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>742305</t>
+          <t>741787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754118</t>
+          <t>754152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>759983</t>
+          <t>761279</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>776333</t>
+          <t>777363</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1507327</t>
+          <t>1507274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1528037</t>
+          <t>1527628</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>10804</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28503</t>
+          <t>27635</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32247</t>
+          <t>33729</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>27235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53621</t>
+          <t>52557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>909064</t>
+          <t>909932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>926385</t>
+          <t>926763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1011532</t>
+          <t>1010050</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1031140</t>
+          <t>1030901</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1927725</t>
+          <t>1928789</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1953504</t>
+          <t>1954111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36588</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65709</t>
+          <t>64386</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57185</t>
+          <t>55309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91946</t>
+          <t>91540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99982</t>
+          <t>100489</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145331</t>
+          <t>148343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3328641</t>
+          <t>3329964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3357762</t>
+          <t>3358014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3452596</t>
+          <t>3453002</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3487357</t>
+          <t>3489233</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6793561</t>
+          <t>6790549</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6838910</t>
+          <t>6838403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40878</t>
+          <t>42675</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31654</t>
+          <t>33874</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53488</t>
+          <t>54443</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>41676</t>
+          <t>44486</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34814</t>
+          <t>35749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>53682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>82555</t>
+          <t>87161</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70057</t>
+          <t>74810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95270</t>
+          <t>101808</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>594563</t>
+          <t>648035</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>581953</t>
+          <t>636267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603787</t>
+          <t>656836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>633094</t>
+          <t>687621</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>623889</t>
+          <t>678425</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>639956</t>
+          <t>696358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1227657</t>
+          <t>1335655</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1214942</t>
+          <t>1321008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1240155</t>
+          <t>1348006</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674770</t>
+          <t>732107</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674770</t>
+          <t>732107</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674770</t>
+          <t>732107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310212</t>
+          <t>1422816</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310212</t>
+          <t>1422816</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310212</t>
+          <t>1422816</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48115</t>
+          <t>50457</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22810</t>
+          <t>38973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65611</t>
+          <t>62421</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46066</t>
+          <t>48730</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>39886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56571</t>
+          <t>60975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>94181</t>
+          <t>99187</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62422</t>
+          <t>84212</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114341</t>
+          <t>116222</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1144749</t>
+          <t>998460</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1127253</t>
+          <t>986496</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1170054</t>
+          <t>1009944</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>911211</t>
+          <t>1020780</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>900706</t>
+          <t>1008535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>921275</t>
+          <t>1029624</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2055961</t>
+          <t>2019240</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2035801</t>
+          <t>2002205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2087720</t>
+          <t>2034215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957277</t>
+          <t>1069510</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957277</t>
+          <t>1069510</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957277</t>
+          <t>1069510</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150142</t>
+          <t>2118427</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150142</t>
+          <t>2118427</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150142</t>
+          <t>2118427</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>28878</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>19420</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35059</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28085</t>
+          <t>31873</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41333</t>
+          <t>43024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>52333</t>
+          <t>60751</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34002</t>
+          <t>48679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68277</t>
+          <t>75867</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>677545</t>
+          <t>771171</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>666734</t>
+          <t>759892</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>685842</t>
+          <t>780629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>904650</t>
+          <t>779696</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>891402</t>
+          <t>768545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>917959</t>
+          <t>787285</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1582195</t>
+          <t>1550867</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1566251</t>
+          <t>1535751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1600526</t>
+          <t>1562939</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>701793</t>
+          <t>800049</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>701793</t>
+          <t>800049</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>701793</t>
+          <t>800049</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932735</t>
+          <t>811569</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932735</t>
+          <t>811569</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932735</t>
+          <t>811569</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634528</t>
+          <t>1611618</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634528</t>
+          <t>1611618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634528</t>
+          <t>1611618</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40895</t>
+          <t>42100</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30559</t>
+          <t>31610</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52852</t>
+          <t>54189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44573</t>
+          <t>49422</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33813</t>
+          <t>40809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55781</t>
+          <t>62848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>85468</t>
+          <t>91522</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70037</t>
+          <t>75329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100422</t>
+          <t>106928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>885936</t>
+          <t>947962</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873979</t>
+          <t>935873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>896272</t>
+          <t>958452</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1046549</t>
+          <t>1067373</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1035341</t>
+          <t>1053947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1057309</t>
+          <t>1075986</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1932485</t>
+          <t>2015335</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1917531</t>
+          <t>1999929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1947916</t>
+          <t>2031528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091122</t>
+          <t>1116795</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091122</t>
+          <t>1116795</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091122</t>
+          <t>1116795</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2017953</t>
+          <t>2106857</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2017953</t>
+          <t>2106857</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2017953</t>
+          <t>2106857</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>154136</t>
+          <t>164110</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118802</t>
+          <t>143078</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179133</t>
+          <t>185982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>160400</t>
+          <t>174510</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>130509</t>
+          <t>154437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181385</t>
+          <t>193746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>314536</t>
+          <t>338620</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272030</t>
+          <t>307362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>351359</t>
+          <t>366562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3302794</t>
+          <t>3365628</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3277797</t>
+          <t>3343756</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3338128</t>
+          <t>3386660</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3495504</t>
+          <t>3555471</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3474519</t>
+          <t>3536235</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3525395</t>
+          <t>3575544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6798298</t>
+          <t>6921099</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6761475</t>
+          <t>6893157</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6840804</t>
+          <t>6952357</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456930</t>
+          <t>3529738</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456930</t>
+          <t>3529738</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456930</t>
+          <t>3529738</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3655904</t>
+          <t>3729981</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3655904</t>
+          <t>3729981</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3655904</t>
+          <t>3729981</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7112834</t>
+          <t>7259719</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7112834</t>
+          <t>7259719</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7112834</t>
+          <t>7259719</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
